--- a/data/trans_bre/P1410-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1410-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,93%</t>
+          <t>-4,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,25</t>
+          <t>-4,57; 0,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,87</t>
+          <t>-3,17; 1,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,33</t>
+          <t>0,13; 5,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,85</t>
+          <t>-3,7; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 3,34</t>
+          <t>-39,66; 1,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 22,84</t>
+          <t>-27,66; 22,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 77,06</t>
+          <t>1,52; 88,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 15,74</t>
+          <t>-24,58; 19,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-50,62%</t>
+          <t>-45,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,27</t>
+          <t>-1,54; 0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,51</t>
+          <t>-1,25; 0,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,48</t>
+          <t>-1,53; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,57</t>
+          <t>-2,72; -0,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 21,67</t>
+          <t>-62,95; 20,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 40,83</t>
+          <t>-58,52; 33,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 21,05</t>
+          <t>-44,48; 27,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,37; -22,73</t>
+          <t>-61,48; -22,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-41,62%</t>
+          <t>-45,73%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,81</t>
+          <t>-4,05; -0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,77</t>
+          <t>-1,04; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,7</t>
+          <t>-1,61; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,1</t>
+          <t>-3,7; -0,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,06</t>
+          <t>-100,0; -29,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 184,24</t>
+          <t>-61,95; 222,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 0,4</t>
+          <t>-66,83; -11,81</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>-19,1%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,25</t>
+          <t>-1,77; 0,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,3</t>
+          <t>-0,72; 1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,66</t>
+          <t>-0,24; 1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,29</t>
+          <t>-1,91; -0,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 6,14</t>
+          <t>-35,35; 3,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 39,21</t>
+          <t>-16,48; 35,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 48,22</t>
+          <t>-5,5; 54,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 5,55</t>
+          <t>-32,26; -2,37</t>
         </is>
       </c>
     </row>
